--- a/output/graficos_educacion_tasas/comunal_e_rezmat_a_2023_magallanes.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_rezmat_a_2023_magallanes.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 17:49</t>
+    <t xml:space="preserve">2026-09-09 20:55</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_rezmat_a_2023_magallanes.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_rezmat_a_2023_magallanes.xlsx
@@ -24,21 +24,21 @@
     <t xml:space="preserve">Valor (%)</t>
   </si>
   <si>
+    <t xml:space="preserve">Punta Arenas</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cabo de Hornos</t>
   </si>
   <si>
+    <t xml:space="preserve">Porvenir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primavera</t>
+  </si>
+  <si>
     <t xml:space="preserve">Natales</t>
   </si>
   <si>
-    <t xml:space="preserve">Porvenir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primavera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Punta Arenas</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:55</t>
+    <t xml:space="preserve">2026-09-18 10:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -460,7 +460,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.52</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="3">
@@ -468,7 +468,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>2.4</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="4">
@@ -492,7 +492,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1.63</v>
+        <v>2.4</v>
       </c>
     </row>
   </sheetData>
